--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9186,6 +9186,42 @@
       <c r="J243" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="C244" t="n">
+        <v>355.73</v>
+      </c>
+      <c r="D244" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="E244" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="F244" t="n">
+        <v>395.97</v>
+      </c>
+      <c r="G244" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="H244" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="I244" t="n">
+        <v>388.42</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11703,6 +11739,16 @@
       </c>
       <c r="B250" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -11871,28 +11917,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.366222708756553</v>
+        <v>-1.369240129300423</v>
       </c>
       <c r="J2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3275000530448505</v>
+        <v>0.3304363476382061</v>
       </c>
       <c r="M2" t="n">
-        <v>11.61506564935196</v>
+        <v>11.58099298681733</v>
       </c>
       <c r="N2" t="n">
-        <v>238.5528932718266</v>
+        <v>237.633152715817</v>
       </c>
       <c r="O2" t="n">
-        <v>15.4451575994493</v>
+        <v>15.41535444664887</v>
       </c>
       <c r="P2" t="n">
-        <v>416.9195117666259</v>
+        <v>416.9491648720988</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11949,28 +11995,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.266872895830121</v>
+        <v>-2.26418001657971</v>
       </c>
       <c r="J3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6560014802825231</v>
+        <v>0.6574617163960097</v>
       </c>
       <c r="M3" t="n">
-        <v>10.01426379214783</v>
+        <v>9.991433930684678</v>
       </c>
       <c r="N3" t="n">
-        <v>167.7130677693598</v>
+        <v>167.0722378615687</v>
       </c>
       <c r="O3" t="n">
-        <v>12.95040801555533</v>
+        <v>12.92564264791383</v>
       </c>
       <c r="P3" t="n">
-        <v>413.2120255514411</v>
+        <v>413.1855618115424</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12027,28 +12073,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.249569833538176</v>
+        <v>-2.247702625275919</v>
       </c>
       <c r="J4" t="n">
+        <v>243</v>
+      </c>
+      <c r="K4" t="n">
         <v>242</v>
       </c>
-      <c r="K4" t="n">
-        <v>241</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.678621714339853</v>
+        <v>0.6802183472176397</v>
       </c>
       <c r="M4" t="n">
-        <v>9.590926008955158</v>
+        <v>9.562418385316784</v>
       </c>
       <c r="N4" t="n">
-        <v>148.6377168748573</v>
+        <v>148.0471515938307</v>
       </c>
       <c r="O4" t="n">
-        <v>12.19170688931034</v>
+        <v>12.16746282483866</v>
       </c>
       <c r="P4" t="n">
-        <v>430.936424094609</v>
+        <v>430.9179943387593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12105,28 +12151,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.974133369035521</v>
+        <v>-1.972912158702063</v>
       </c>
       <c r="J5" t="n">
+        <v>243</v>
+      </c>
+      <c r="K5" t="n">
         <v>242</v>
       </c>
-      <c r="K5" t="n">
-        <v>241</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6501184533063897</v>
+        <v>0.6518985903795235</v>
       </c>
       <c r="M5" t="n">
-        <v>8.753323729859796</v>
+        <v>8.72450931752156</v>
       </c>
       <c r="N5" t="n">
-        <v>130.0836793396882</v>
+        <v>129.5562556791256</v>
       </c>
       <c r="O5" t="n">
-        <v>11.40542324246181</v>
+        <v>11.38227814100172</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9311309752408</v>
+        <v>439.9190773609001</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12183,28 +12229,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.549989913759034</v>
+        <v>-1.550689237957054</v>
       </c>
       <c r="J6" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K6" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5665821322734295</v>
+        <v>0.5690417944375954</v>
       </c>
       <c r="M6" t="n">
-        <v>8.216902683243323</v>
+        <v>8.186905140922567</v>
       </c>
       <c r="N6" t="n">
-        <v>114.383265243695</v>
+        <v>113.9158802460267</v>
       </c>
       <c r="O6" t="n">
-        <v>10.6950112315834</v>
+        <v>10.67313825667159</v>
       </c>
       <c r="P6" t="n">
-        <v>438.5614686932421</v>
+        <v>438.5683411639178</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12261,28 +12307,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9936168036504008</v>
+        <v>-0.9975557372914857</v>
       </c>
       <c r="J7" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K7" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3869790120272492</v>
+        <v>0.3907753151274923</v>
       </c>
       <c r="M7" t="n">
-        <v>7.664722094320311</v>
+        <v>7.655562671049325</v>
       </c>
       <c r="N7" t="n">
-        <v>97.33893634826011</v>
+        <v>97.04394593910479</v>
       </c>
       <c r="O7" t="n">
-        <v>9.866049683042352</v>
+        <v>9.851088566199412</v>
       </c>
       <c r="P7" t="n">
-        <v>422.8472235235579</v>
+        <v>422.885932617306</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12339,28 +12385,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8909900039871413</v>
+        <v>-0.8963464869971106</v>
       </c>
       <c r="J8" t="n">
+        <v>243</v>
+      </c>
+      <c r="K8" t="n">
         <v>242</v>
       </c>
-      <c r="K8" t="n">
-        <v>241</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3201269248943674</v>
+        <v>0.3243437157519535</v>
       </c>
       <c r="M8" t="n">
-        <v>7.537844532030602</v>
+        <v>7.540632467174398</v>
       </c>
       <c r="N8" t="n">
-        <v>105.2785219319838</v>
+        <v>105.0387258478079</v>
       </c>
       <c r="O8" t="n">
-        <v>10.2605322440887</v>
+        <v>10.24884021964475</v>
       </c>
       <c r="P8" t="n">
-        <v>422.2709548581068</v>
+        <v>422.3234576975618</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12417,28 +12463,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4575989120278776</v>
+        <v>-0.4622220982885678</v>
       </c>
       <c r="J9" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K9" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1908472444369351</v>
+        <v>0.1949911500189269</v>
       </c>
       <c r="M9" t="n">
-        <v>5.793686894345407</v>
+        <v>5.796372338993226</v>
       </c>
       <c r="N9" t="n">
-        <v>55.25548550675587</v>
+        <v>55.17354631547996</v>
       </c>
       <c r="O9" t="n">
-        <v>7.433403359616366</v>
+        <v>7.427889761936425</v>
       </c>
       <c r="P9" t="n">
-        <v>406.7092350262086</v>
+        <v>406.7546684776669</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12480,7 +12526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25107,6 +25153,58 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-35.177310701307036,173.11795440139448</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>-35.177944256766644,173.11846490442736</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-35.17829852945076,173.11926010778126</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-35.1785213241891,173.12009660097956</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-35.178674405590634,173.12089316132727</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-35.178790464965275,173.12172852178762</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-35.17880790452991,173.12259511241552</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-35.17876534703921,173.12346840403953</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9222,6 +9222,42 @@
       <c r="J244" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="C245" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="D245" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="E245" t="n">
+        <v>389.93</v>
+      </c>
+      <c r="F245" t="n">
+        <v>399.08</v>
+      </c>
+      <c r="G245" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="H245" t="n">
+        <v>395.49</v>
+      </c>
+      <c r="I245" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11749,6 +11785,16 @@
       </c>
       <c r="B251" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -11917,28 +11963,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.369240129300423</v>
+        <v>-1.362254663235736</v>
       </c>
       <c r="J2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3304363476382061</v>
+        <v>0.3298887209160936</v>
       </c>
       <c r="M2" t="n">
-        <v>11.58099298681733</v>
+        <v>11.57604412935929</v>
       </c>
       <c r="N2" t="n">
-        <v>237.633152715817</v>
+        <v>236.9925964051467</v>
       </c>
       <c r="O2" t="n">
-        <v>15.41535444664887</v>
+        <v>15.3945638588804</v>
       </c>
       <c r="P2" t="n">
-        <v>416.9491648720988</v>
+        <v>416.8801727244693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11995,28 +12041,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.26418001657971</v>
+        <v>-2.261536834648173</v>
       </c>
       <c r="J3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6574617163960097</v>
+        <v>0.6589325823631906</v>
       </c>
       <c r="M3" t="n">
-        <v>9.991433930684678</v>
+        <v>9.968312590254005</v>
       </c>
       <c r="N3" t="n">
-        <v>167.0722378615687</v>
+        <v>166.4352425457098</v>
       </c>
       <c r="O3" t="n">
-        <v>12.92564264791383</v>
+        <v>12.90097835614454</v>
       </c>
       <c r="P3" t="n">
-        <v>413.1855618115424</v>
+        <v>413.1594563525302</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12073,28 +12119,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.247702625275919</v>
+        <v>-2.246082235911345</v>
       </c>
       <c r="J4" t="n">
+        <v>244</v>
+      </c>
+      <c r="K4" t="n">
         <v>243</v>
       </c>
-      <c r="K4" t="n">
-        <v>242</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6802183472176397</v>
+        <v>0.6818689113251535</v>
       </c>
       <c r="M4" t="n">
-        <v>9.562418385316784</v>
+        <v>9.532636837955703</v>
       </c>
       <c r="N4" t="n">
-        <v>148.0471515938307</v>
+        <v>147.4557755721027</v>
       </c>
       <c r="O4" t="n">
-        <v>12.16746282483866</v>
+        <v>12.14313697411434</v>
       </c>
       <c r="P4" t="n">
-        <v>430.9179943387593</v>
+        <v>430.9019206554108</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12151,28 +12197,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.972912158702063</v>
+        <v>-1.970366507831746</v>
       </c>
       <c r="J5" t="n">
+        <v>244</v>
+      </c>
+      <c r="K5" t="n">
         <v>243</v>
       </c>
-      <c r="K5" t="n">
-        <v>242</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6518985903795235</v>
+        <v>0.6533128048648607</v>
       </c>
       <c r="M5" t="n">
-        <v>8.72450931752156</v>
+        <v>8.703751084405445</v>
       </c>
       <c r="N5" t="n">
-        <v>129.5562556791256</v>
+        <v>129.06721066165</v>
       </c>
       <c r="O5" t="n">
-        <v>11.38227814100172</v>
+        <v>11.36077509070794</v>
       </c>
       <c r="P5" t="n">
-        <v>439.9190773609001</v>
+        <v>439.893825414115</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12229,28 +12275,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.550689237957054</v>
+        <v>-1.548850437941078</v>
       </c>
       <c r="J6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5690417944375954</v>
+        <v>0.5706557498244229</v>
       </c>
       <c r="M6" t="n">
-        <v>8.186905140922567</v>
+        <v>8.162782796198652</v>
       </c>
       <c r="N6" t="n">
-        <v>113.9158802460267</v>
+        <v>113.472110117033</v>
       </c>
       <c r="O6" t="n">
-        <v>10.67313825667159</v>
+        <v>10.65232885884739</v>
       </c>
       <c r="P6" t="n">
-        <v>438.5683411639178</v>
+        <v>438.5501802050084</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12307,28 +12353,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9975557372914857</v>
+        <v>-0.9967322798179776</v>
       </c>
       <c r="J7" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K7" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3907753151274923</v>
+        <v>0.3925530766095183</v>
       </c>
       <c r="M7" t="n">
-        <v>7.655562671049325</v>
+        <v>7.628226217244487</v>
       </c>
       <c r="N7" t="n">
-        <v>97.04394593910479</v>
+        <v>96.6508571004164</v>
       </c>
       <c r="O7" t="n">
-        <v>9.851088566199412</v>
+        <v>9.831116777885226</v>
       </c>
       <c r="P7" t="n">
-        <v>422.885932617306</v>
+        <v>422.8777997169307</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12385,28 +12431,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8963464869971106</v>
+        <v>-0.8983699729111635</v>
       </c>
       <c r="J8" t="n">
+        <v>244</v>
+      </c>
+      <c r="K8" t="n">
         <v>243</v>
       </c>
-      <c r="K8" t="n">
-        <v>242</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3243437157519535</v>
+        <v>0.3272944567945013</v>
       </c>
       <c r="M8" t="n">
-        <v>7.540632467174398</v>
+        <v>7.522419503832472</v>
       </c>
       <c r="N8" t="n">
-        <v>105.0387258478079</v>
+        <v>104.6344402158637</v>
       </c>
       <c r="O8" t="n">
-        <v>10.24884021964475</v>
+        <v>10.22909772247111</v>
       </c>
       <c r="P8" t="n">
-        <v>422.3234576975618</v>
+        <v>422.3433910631034</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12463,28 +12509,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4622220982885678</v>
+        <v>-0.4632083726047443</v>
       </c>
       <c r="J9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1949911500189269</v>
+        <v>0.1970877864334494</v>
       </c>
       <c r="M9" t="n">
-        <v>5.796372338993226</v>
+        <v>5.778216082525648</v>
       </c>
       <c r="N9" t="n">
-        <v>55.17354631547996</v>
+        <v>54.95407038033858</v>
       </c>
       <c r="O9" t="n">
-        <v>7.427889761936425</v>
+        <v>7.413101266024806</v>
       </c>
       <c r="P9" t="n">
-        <v>406.7546684776669</v>
+        <v>406.7644094430648</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12526,7 +12572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25205,6 +25251,58 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-35.1772257900095,173.1180492933129</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-35.1779460105195,173.11846300939592</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-35.17830244604158,173.11925677223633</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-35.178508825792086,173.12010345271472</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-35.17864702587884,173.1209005480989</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-35.17873648342745,173.1217329342896</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-35.17877095616191,173.12259355944124</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-35.178724333904164,173.1234635234593</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0061/nzd0061.xlsx
+++ b/data/nzd0061/nzd0061.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9256,6 +9256,42 @@
         <v>392.99</v>
       </c>
       <c r="J245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="C246" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="D246" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="E246" t="n">
+        <v>390.89</v>
+      </c>
+      <c r="F246" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="G246" t="n">
+        <v>395.01</v>
+      </c>
+      <c r="H246" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="I246" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="J246" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9272,7 +9308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11795,6 +11831,16 @@
       </c>
       <c r="B252" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -11963,28 +12009,28 @@
         <v>0.0315</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.362254663235736</v>
+        <v>-1.355380660467426</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3298887209160936</v>
+        <v>0.3293508197548163</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57604412935929</v>
+        <v>11.57059546466237</v>
       </c>
       <c r="N2" t="n">
-        <v>236.9925964051467</v>
+        <v>236.3529317363041</v>
       </c>
       <c r="O2" t="n">
-        <v>15.3945638588804</v>
+        <v>15.37377415393839</v>
       </c>
       <c r="P2" t="n">
-        <v>416.8801727244693</v>
+        <v>416.8121460610993</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12041,28 +12087,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.261536834648173</v>
+        <v>-2.258877530088232</v>
       </c>
       <c r="J3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6589325823631906</v>
+        <v>0.6603743156003705</v>
       </c>
       <c r="M3" t="n">
-        <v>9.968312590254005</v>
+        <v>9.945431854214341</v>
       </c>
       <c r="N3" t="n">
-        <v>166.4352425457098</v>
+        <v>165.8049526742807</v>
       </c>
       <c r="O3" t="n">
-        <v>12.90097835614454</v>
+        <v>12.87652719774554</v>
       </c>
       <c r="P3" t="n">
-        <v>413.1594563525302</v>
+        <v>413.1331392819392</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12119,28 +12165,28 @@
         <v>0.0522</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.246082235911345</v>
+        <v>-2.244423004429869</v>
       </c>
       <c r="J4" t="n">
+        <v>245</v>
+      </c>
+      <c r="K4" t="n">
         <v>244</v>
       </c>
-      <c r="K4" t="n">
-        <v>243</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6818689113251535</v>
+        <v>0.6834858650095978</v>
       </c>
       <c r="M4" t="n">
-        <v>9.532636837955703</v>
+        <v>9.503321081898623</v>
       </c>
       <c r="N4" t="n">
-        <v>147.4557755721027</v>
+        <v>146.8704688849333</v>
       </c>
       <c r="O4" t="n">
-        <v>12.14313697411434</v>
+        <v>12.11901270256506</v>
       </c>
       <c r="P4" t="n">
-        <v>430.9019206554108</v>
+        <v>430.8854288624003</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12197,28 +12243,28 @@
         <v>0.0455</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.970366507831746</v>
+        <v>-1.967081863688771</v>
       </c>
       <c r="J5" t="n">
+        <v>245</v>
+      </c>
+      <c r="K5" t="n">
         <v>244</v>
       </c>
-      <c r="K5" t="n">
-        <v>243</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6533128048648607</v>
+        <v>0.6544794917428234</v>
       </c>
       <c r="M5" t="n">
-        <v>8.703751084405445</v>
+        <v>8.687771459498919</v>
       </c>
       <c r="N5" t="n">
-        <v>129.06721066165</v>
+        <v>128.612784932196</v>
       </c>
       <c r="O5" t="n">
-        <v>11.36077509070794</v>
+        <v>11.34075768774715</v>
       </c>
       <c r="P5" t="n">
-        <v>439.893825414115</v>
+        <v>439.8611779674365</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12275,28 +12321,28 @@
         <v>0.0311</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.548850437941078</v>
+        <v>-1.547073645974351</v>
       </c>
       <c r="J6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5706557498244229</v>
+        <v>0.5722674587845018</v>
       </c>
       <c r="M6" t="n">
-        <v>8.162782796198652</v>
+        <v>8.138507797522037</v>
       </c>
       <c r="N6" t="n">
-        <v>113.472110117033</v>
+        <v>113.0308497000291</v>
       </c>
       <c r="O6" t="n">
-        <v>10.65232885884739</v>
+        <v>10.63159676154194</v>
       </c>
       <c r="P6" t="n">
-        <v>438.5501802050084</v>
+        <v>438.5325966757209</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12353,28 +12399,28 @@
         <v>0.0262</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9967322798179776</v>
+        <v>-0.9974229946467641</v>
       </c>
       <c r="J7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3925530766095183</v>
+        <v>0.3950409562301228</v>
       </c>
       <c r="M7" t="n">
-        <v>7.628226217244487</v>
+        <v>7.601030607281173</v>
       </c>
       <c r="N7" t="n">
-        <v>96.6508571004164</v>
+        <v>96.25967200070619</v>
       </c>
       <c r="O7" t="n">
-        <v>9.831116777885226</v>
+        <v>9.811201353591017</v>
       </c>
       <c r="P7" t="n">
-        <v>422.8777997169307</v>
+        <v>422.8846351848125</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12431,28 +12477,28 @@
         <v>0.0267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8983699729111635</v>
+        <v>-0.9014317060018224</v>
       </c>
       <c r="J8" t="n">
+        <v>245</v>
+      </c>
+      <c r="K8" t="n">
         <v>244</v>
       </c>
-      <c r="K8" t="n">
-        <v>243</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3272944567945013</v>
+        <v>0.3306676274005157</v>
       </c>
       <c r="M8" t="n">
-        <v>7.522419503832472</v>
+        <v>7.51083970197111</v>
       </c>
       <c r="N8" t="n">
-        <v>104.6344402158637</v>
+        <v>104.2706214196692</v>
       </c>
       <c r="O8" t="n">
-        <v>10.22909772247111</v>
+        <v>10.21129871366367</v>
       </c>
       <c r="P8" t="n">
-        <v>422.3433910631034</v>
+        <v>422.373612560408</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12509,28 +12555,28 @@
         <v>0.035</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4632083726047443</v>
+        <v>-0.4648925340290325</v>
       </c>
       <c r="J9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1970877864334494</v>
+        <v>0.1996271536570153</v>
       </c>
       <c r="M9" t="n">
-        <v>5.778216082525648</v>
+        <v>5.764120943033701</v>
       </c>
       <c r="N9" t="n">
-        <v>54.95407038033858</v>
+        <v>54.74943608474025</v>
       </c>
       <c r="O9" t="n">
-        <v>7.413101266024806</v>
+        <v>7.399286187514323</v>
       </c>
       <c r="P9" t="n">
-        <v>406.7644094430648</v>
+        <v>406.7810762798603</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -12572,7 +12618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25303,6 +25349,58 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-35.1772257900095,173.1180492933129</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-35.1779460105195,173.11846300939592</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-35.17830244604158,173.11925677223633</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-35.17850093206743,173.12010778012535</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-35.17864790625541,173.12090031058221</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-35.1787545672427,173.12173145610208</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-35.178784113385674,173.12259411245142</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-35.17873294935489,173.12346454870112</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
